--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5588,7 +5451,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7740,7 +7603,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -8262,1899 +8125,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Deep Water South 第6B期 - 1A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>61 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>23 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>15 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>23 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2642呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$8,686万
-$51,217/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$8,644万
-$50,964/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$7,975万
-$47,021/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$7,836万
-$46,200/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-$6,927万
-$43,459/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$7,937万
-$46,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$8,293万
-$48,895/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$7,552万
-$44,530/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-$6,927万
-$43,457/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$7,552万
-$44,530/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-$6,942万
-$43,549/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-$6,331万
-$39,720/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$5,851万
-$34,500/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-$5,420万
-$34,000/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-$5,902万
-$34,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 1594呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 1620呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 1520呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Deep Water South 第6B期 - 1B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>93 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>21 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>15 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>57 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-$3,704万
-$40,168/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-$3,942万
-$42,757/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-$3,715万
-$40,463/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-$3,710万
-$40,410/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-$3,612万
-$39,350/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-$3,534万
-$38,500/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-$3,689万
-$40,184/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-$3,488万
-$38,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-$3,630万
-$39,376/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-$3,411万
-$37,000/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-$3,479万
-$37,898/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-$3,135万
-$34,000/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-$3,011万
-$32,800/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-$3,239万
-$35,130/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-$3,024万
-$32,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 918呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 862呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 870呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 874呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>C | 837呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +143,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +224,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8125,4 +8305,1899 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2642呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$8686万
+$51,217/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$8644万
+$50,964/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$7975万
+$47,021/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$7836万
+$46,200/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+$6927万
+$43,459/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$7937万
+$46,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$8293万
+$48,895/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$7552万
+$44,530/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+$6927万
+$43,457/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$7552万
+$44,530/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+$6942万
+$43,549/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+$6331万
+$39,720/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$5851万
+$34,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+$5420万
+$34,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+$5902万
+$34,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 1594呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 1620呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 1520呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+$3704万
+$40,168/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+$3942万
+$42,757/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+$3715万
+$40,463/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+$3710万
+$40,410/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+$3612万
+$39,350/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+$3534万
+$38,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+$3689万
+$40,184/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+$3488万
+$38,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+$3630万
+$39,376/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+$3411万
+$37,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+$3479万
+$37,898/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+$3135万
+$34,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+$3011万
+$32,800/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+$3239万
+$35,130/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+$3024万
+$32,800/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 918呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 862呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 870呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 874呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 837呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:N156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -657,6 +657,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -714,6 +718,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -764,6 +788,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -814,6 +858,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -864,6 +928,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -914,6 +998,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -964,6 +1068,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1014,6 +1138,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1064,6 +1208,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1114,6 +1278,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1164,6 +1348,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1214,6 +1418,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1260,6 +1484,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1310,6 +1554,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1356,6 +1620,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1406,6 +1690,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1456,6 +1760,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1506,6 +1830,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1552,6 +1896,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1598,6 +1962,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1644,6 +2028,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1694,6 +2098,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1740,6 +2164,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1790,6 +2234,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1836,6 +2300,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1886,6 +2370,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1936,6 +2440,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1986,6 +2510,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2036,6 +2580,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2086,6 +2650,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2136,6 +2720,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2182,6 +2786,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2228,6 +2852,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2274,6 +2918,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2320,6 +2984,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2370,6 +3054,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2420,6 +3124,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2470,6 +3194,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2520,6 +3264,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2570,6 +3334,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2620,6 +3404,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2670,6 +3474,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2720,6 +3544,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2766,6 +3610,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2816,6 +3680,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2866,6 +3750,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2916,6 +3820,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2966,6 +3890,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3016,6 +3960,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3066,6 +4030,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3116,6 +4100,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3166,6 +4170,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3216,6 +4240,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3262,6 +4306,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3308,6 +4372,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3358,6 +4442,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3404,6 +4508,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3454,6 +4578,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3504,6 +4648,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3554,6 +4718,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3604,6 +4788,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3654,6 +4858,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3704,6 +4928,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3754,6 +4998,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3804,6 +5068,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3854,6 +5138,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3904,6 +5208,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3954,6 +5278,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4004,6 +5348,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4054,6 +5418,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4104,6 +5488,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4154,6 +5558,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4204,6 +5628,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4254,6 +5698,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4304,6 +5768,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4354,6 +5838,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4404,6 +5908,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4454,6 +5978,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4504,6 +6048,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4554,6 +6118,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4604,6 +6188,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4654,6 +6258,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4704,6 +6328,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4754,6 +6398,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4804,6 +6468,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4854,6 +6538,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4904,6 +6608,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4954,6 +6678,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5000,6 +6744,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5050,6 +6814,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5100,6 +6884,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5146,6 +6950,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5196,6 +7020,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5246,6 +7090,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5296,6 +7160,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5346,6 +7230,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5396,6 +7300,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5446,6 +7370,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5496,6 +7440,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5546,6 +7510,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5596,6 +7580,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5642,6 +7646,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5692,6 +7716,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5742,6 +7786,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5792,6 +7856,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5842,6 +7926,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5892,6 +7996,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5938,6 +8062,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5988,6 +8132,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6038,6 +8202,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6084,6 +8268,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6134,6 +8338,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6184,6 +8408,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6234,6 +8478,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6284,6 +8548,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6334,6 +8618,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6384,6 +8688,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6434,6 +8758,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6484,6 +8828,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6530,6 +8894,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6580,6 +8964,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6630,6 +9034,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6676,6 +9100,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6726,6 +9170,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6772,6 +9236,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6818,6 +9302,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6868,6 +9372,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6914,6 +9438,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6964,6 +9508,26 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7014,6 +9578,26 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7064,6 +9648,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7114,6 +9718,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7164,6 +9788,26 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7214,6 +9858,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7264,6 +9928,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7314,6 +9998,26 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7364,6 +10068,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7414,6 +10138,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7464,6 +10208,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7510,6 +10274,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7556,6 +10340,26 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7606,6 +10410,26 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7652,6 +10476,26 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7698,6 +10542,26 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7748,6 +10612,26 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7794,6 +10678,26 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7844,6 +10748,26 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7894,6 +10818,26 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7944,6 +10888,26 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7994,6 +10958,26 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -8044,6 +11028,26 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8094,6 +11098,26 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8144,6 +11168,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8194,6 +11238,26 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8244,6 +11308,26 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8294,13 +11378,33 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8528,7 +11632,7 @@
           <t>A | 1696呎 (4+房)
 $8686万
 $51,217/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -8551,7 +11655,7 @@
           <t>A | 1696呎 (4+房)
 $8644万
 $50,964/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -8597,7 +11701,7 @@
           <t>A | 1696呎 (4+房)
 $7975万
 $47,021/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -8620,7 +11724,7 @@
           <t>A | 1696呎 (4+房)
 $7836万
 $46,200/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -8628,7 +11732,7 @@
           <t>B | 1594呎 (4+房)
 $6927万
 $43,459/呎
-(26年-04月)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
     </row>
@@ -8643,7 +11747,7 @@
           <t>A | 1696呎 (4+房)
 $7937万
 $46,800/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -8666,7 +11770,7 @@
           <t>A | 1696呎 (4+房)
 $8293万
 $48,895/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -8758,7 +11862,7 @@
           <t>A | 1696呎 (4+房)
 $7552万
 $44,530/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -8766,7 +11870,7 @@
           <t>B | 1594呎 (4+房)
 $6927万
 $43,457/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -8781,7 +11885,7 @@
           <t>A | 1696呎 (4+房)
 $7552万
 $44,530/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -8789,7 +11893,7 @@
           <t>B | 1594呎 (4+房)
 $6942万
 $43,549/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -8904,7 +12008,7 @@
           <t>B | 1594呎 (4+房)
 $6331万
 $39,720/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -9011,7 +12115,7 @@
           <t>A | 1696呎 (4+房)
 $5851万
 $34,500/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -9019,7 +12123,7 @@
           <t>B | 1594呎 (4+房)
 $5420万
 $34,000/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -9034,7 +12138,7 @@
           <t>A | 1696呎 (4+房)
 $5902万
 $34,800/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -9499,7 +12603,7 @@
           <t>B | 922呎 (3房)
 $3704万
 $40,168/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -9530,7 +12634,7 @@
           <t>B | 922呎 (3房)
 $3942万
 $42,757/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9615,7 +12719,7 @@
           <t>A | 918呎 (3房)
 $3715万
 $40,463/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -9677,7 +12781,7 @@
           <t>A | 918呎 (3房)
 $3710万
 $40,410/呎
-(26年-07月)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -9708,7 +12812,7 @@
           <t>A | 918呎 (3房)
 $3612万
 $39,350/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -9801,7 +12905,7 @@
           <t>A | 918呎 (3房)
 $3534万
 $38,500/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -9832,7 +12936,7 @@
           <t>A | 918呎 (3房)
 $3689万
 $40,184/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -9863,7 +12967,7 @@
           <t>A | 918呎 (3房)
 $3488万
 $38,000/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -9871,7 +12975,7 @@
           <t>B | 922呎 (3房)
 $3630万
 $39,376/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -9902,7 +13006,7 @@
           <t>B | 922呎 (3房)
 $3411万
 $37,000/呎
-(26年-07月)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10018,7 +13122,7 @@
           <t>A | 918呎 (3房)
 $3479万
 $37,898/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -10026,7 +13130,7 @@
           <t>B | 922呎 (3房)
 $3135万
 $34,000/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -10049,7 +13153,7 @@
           <t>A | 918呎 (3房)
 $3011万
 $32,800/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -10057,7 +13161,7 @@
           <t>B | 922呎 (3房)
 $3239万
 $35,130/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -10088,7 +13192,7 @@
           <t>B | 922呎 (3房)
 $3024万
 $32,800/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -1609,14 +1609,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>86435120</v>
+        <v>82166000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>50964</v>
+        <v>48447</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -11653,9 +11653,9 @@
       <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 1696呎 (4+房)
-$8644万
-$50,964/呎
-(26年-04月-01日)</t>
+$8217万
+$48,447/呎
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -9427,7 +9427,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -13006,7 +13006,7 @@
           <t>B | 922呎 (3房)
 $3411万
 $37,000/呎
-(26年-07月-03日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -11632,7 +11632,7 @@
           <t>A | 1696呎 (4+房)
 $8686万
 $51,217/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -11655,7 +11655,7 @@
           <t>A | 1696呎 (4+房)
 $8217万
 $48,447/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -11701,7 +11701,7 @@
           <t>A | 1696呎 (4+房)
 $7975万
 $47,021/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11724,7 +11724,7 @@
           <t>A | 1696呎 (4+房)
 $7836万
 $46,200/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -11732,7 +11732,7 @@
           <t>B | 1594呎 (4+房)
 $6927万
 $43,459/呎
-(26年-04月-10日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
           <t>A | 1696呎 (4+房)
 $7937万
 $46,800/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11770,7 +11770,7 @@
           <t>A | 1696呎 (4+房)
 $8293万
 $48,895/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11862,7 +11862,7 @@
           <t>A | 1696呎 (4+房)
 $7552万
 $44,530/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -11870,7 +11870,7 @@
           <t>B | 1594呎 (4+房)
 $6927万
 $43,457/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -11885,7 +11885,7 @@
           <t>A | 1696呎 (4+房)
 $7552万
 $44,530/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -11893,7 +11893,7 @@
           <t>B | 1594呎 (4+房)
 $6942万
 $43,549/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12008,7 @@
           <t>B | 1594呎 (4+房)
 $6331万
 $39,720/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
           <t>A | 1696呎 (4+房)
 $5851万
 $34,500/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -12123,7 +12123,7 @@
           <t>B | 1594呎 (4+房)
 $5420万
 $34,000/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
           <t>A | 1696呎 (4+房)
 $5902万
 $34,800/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -12603,7 +12603,7 @@
           <t>B | 922呎 (3房)
 $3704万
 $40,168/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -12634,7 +12634,7 @@
           <t>B | 922呎 (3房)
 $3942万
 $42,757/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -12719,7 +12719,7 @@
           <t>A | 918呎 (3房)
 $3715万
 $40,463/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -12781,7 +12781,7 @@
           <t>A | 918呎 (3房)
 $3710万
 $40,410/呎
-(26年-07月-03日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -12812,7 +12812,7 @@
           <t>A | 918呎 (3房)
 $3612万
 $39,350/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -12905,7 +12905,7 @@
           <t>A | 918呎 (3房)
 $3534万
 $38,500/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -12936,7 +12936,7 @@
           <t>A | 918呎 (3房)
 $3689万
 $40,184/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -12967,7 +12967,7 @@
           <t>A | 918呎 (3房)
 $3488万
 $38,000/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -12975,7 +12975,7 @@
           <t>B | 922呎 (3房)
 $3630万
 $39,376/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -13006,7 +13006,7 @@
           <t>B | 922呎 (3房)
 $3411万
 $37,000/呎
-(26年-07月-19日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -13122,7 +13122,7 @@
           <t>A | 918呎 (3房)
 $3479万
 $37,898/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -13130,7 +13130,7 @@
           <t>B | 922呎 (3房)
 $3135万
 $34,000/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -13153,7 +13153,7 @@
           <t>A | 918呎 (3房)
 $3011万
 $32,800/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -13161,7 +13161,7 @@
           <t>B | 922呎 (3房)
 $3239万
 $35,130/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -13192,7 +13192,7 @@
           <t>B | 922呎 (3房)
 $3024万
 $32,800/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -11632,7 +11632,7 @@
           <t>A | 1696呎 (4+房)
 $8686万
 $51,217/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -11655,7 +11655,7 @@
           <t>A | 1696呎 (4+房)
 $8217万
 $48,447/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -11701,7 +11701,7 @@
           <t>A | 1696呎 (4+房)
 $7975万
 $47,021/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11724,7 +11724,7 @@
           <t>A | 1696呎 (4+房)
 $7836万
 $46,200/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -11732,7 +11732,7 @@
           <t>B | 1594呎 (4+房)
 $6927万
 $43,459/呎
-(26年-04月)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
           <t>A | 1696呎 (4+房)
 $7937万
 $46,800/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11770,7 +11770,7 @@
           <t>A | 1696呎 (4+房)
 $8293万
 $48,895/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11862,7 +11862,7 @@
           <t>A | 1696呎 (4+房)
 $7552万
 $44,530/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -11870,7 +11870,7 @@
           <t>B | 1594呎 (4+房)
 $6927万
 $43,457/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -11885,7 +11885,7 @@
           <t>A | 1696呎 (4+房)
 $7552万
 $44,530/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -11893,7 +11893,7 @@
           <t>B | 1594呎 (4+房)
 $6942万
 $43,549/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12008,7 @@
           <t>B | 1594呎 (4+房)
 $6331万
 $39,720/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
           <t>A | 1696呎 (4+房)
 $5851万
 $34,500/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -12123,7 +12123,7 @@
           <t>B | 1594呎 (4+房)
 $5420万
 $34,000/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
           <t>A | 1696呎 (4+房)
 $5902万
 $34,800/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -12603,7 +12603,7 @@
           <t>B | 922呎 (3房)
 $3704万
 $40,168/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -12634,7 +12634,7 @@
           <t>B | 922呎 (3房)
 $3942万
 $42,757/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -12719,7 +12719,7 @@
           <t>A | 918呎 (3房)
 $3715万
 $40,463/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -12781,7 +12781,7 @@
           <t>A | 918呎 (3房)
 $3710万
 $40,410/呎
-(26年-07月)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -12812,7 +12812,7 @@
           <t>A | 918呎 (3房)
 $3612万
 $39,350/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -12905,7 +12905,7 @@
           <t>A | 918呎 (3房)
 $3534万
 $38,500/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -12936,7 +12936,7 @@
           <t>A | 918呎 (3房)
 $3689万
 $40,184/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -12967,7 +12967,7 @@
           <t>A | 918呎 (3房)
 $3488万
 $38,000/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -12975,7 +12975,7 @@
           <t>B | 922呎 (3房)
 $3630万
 $39,376/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -13006,7 +13006,7 @@
           <t>B | 922呎 (3房)
 $3411万
 $37,000/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -13122,7 +13122,7 @@
           <t>A | 918呎 (3房)
 $3479万
 $37,898/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -13130,7 +13130,7 @@
           <t>B | 922呎 (3房)
 $3135万
 $34,000/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -13153,7 +13153,7 @@
           <t>A | 918呎 (3房)
 $3011万
 $32,800/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -13161,7 +13161,7 @@
           <t>B | 922呎 (3房)
 $3239万
 $35,130/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -13192,7 +13192,7 @@
           <t>B | 922呎 (3房)
 $3024万
 $32,800/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -2153,14 +2153,14 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>79372800</v>
+        <v>78000000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>46800</v>
+        <v>45991</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -11745,9 +11745,9 @@
       <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 1696呎 (4+房)
-$7937万
-$46,800/呎
-(26年-06月-23日)</t>
+$7800万
+$45,991/呎
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11885,7 +11885,7 @@
           <t>A | 1696呎 (4+房)
 $7552万
 $44,530/呎
-(26年-06月-24日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -12781,7 +12781,7 @@
           <t>A | 918呎 (3房)
 $3710万
 $40,410/呎
-(26年-07月-03日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
